--- a/events.xlsx
+++ b/events.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="415">
   <si>
     <t>Event</t>
   </si>
@@ -222,16 +222,13 @@
     <t>Mixto</t>
   </si>
   <si>
-    <t>12:54</t>
-  </si>
-  <si>
-    <t>13:00</t>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>13:07</t>
   </si>
   <si>
     <t xml:space="preserve">63;73 </t>
-  </si>
-  <si>
-    <t>13:07</t>
   </si>
   <si>
     <t>13:30</t>
@@ -1453,7 +1450,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1496,9 +1493,18 @@
     </xf>
     <xf borderId="3" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="7" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
@@ -1983,9 +1989,7 @@
       <c r="F5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="13" t="s">
-        <v>20</v>
-      </c>
+      <c r="G5" s="13"/>
       <c r="H5" s="7" t="s">
         <v>21</v>
       </c>
@@ -2253,13 +2257,13 @@
       <c r="A12" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="20" t="s">
         <v>69</v>
       </c>
       <c r="E12" s="17" t="s">
@@ -2268,7 +2272,9 @@
       <c r="F12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="19"/>
+      <c r="G12" s="21" t="s">
+        <v>50</v>
+      </c>
       <c r="H12" s="7" t="s">
         <v>21</v>
       </c>
@@ -2293,16 +2299,16 @@
         <v>15</v>
       </c>
       <c r="B13" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="12" t="s">
+      <c r="E13" s="13" t="s">
         <v>72</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>73</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>19</v>
@@ -2334,23 +2340,21 @@
         <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="17" t="s">
         <v>75</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>76</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="17" t="s">
-        <v>50</v>
-      </c>
+      <c r="G14" s="17"/>
       <c r="H14" s="7" t="s">
         <v>21</v>
       </c>
@@ -2375,21 +2379,21 @@
         <v>37</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="12" t="s">
+      <c r="E15" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="F15" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="G15" s="20"/>
+      <c r="G15" s="22"/>
       <c r="H15" s="7" t="s">
         <v>21</v>
       </c>
@@ -2414,16 +2418,16 @@
         <v>26</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="17" t="s">
         <v>82</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>83</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>57</v>
@@ -2452,24 +2456,24 @@
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="A17" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="C17" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="12" t="s">
+      <c r="E17" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="F17" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="F17" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="20"/>
+      <c r="G17" s="22"/>
       <c r="H17" s="7" t="s">
         <v>21</v>
       </c>
@@ -2494,16 +2498,16 @@
         <v>15</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="17" t="s">
         <v>90</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>91</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>49</v>
@@ -2535,18 +2539,18 @@
         <v>26</v>
       </c>
       <c r="B19" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" s="12" t="s">
+      <c r="E19" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="20"/>
+      <c r="F19" s="22"/>
       <c r="G19" s="13" t="s">
         <v>36</v>
       </c>
@@ -2574,16 +2578,16 @@
         <v>46</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D20" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="17" t="s">
         <v>95</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>96</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>49</v>
@@ -2615,21 +2619,21 @@
         <v>37</v>
       </c>
       <c r="B21" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" s="12" t="s">
+      <c r="E21" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="F21" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G21" s="20"/>
+      <c r="G21" s="22"/>
       <c r="H21" s="7" t="s">
         <v>21</v>
       </c>
@@ -2654,16 +2658,16 @@
         <v>26</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="17" t="s">
         <v>102</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>103</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>57</v>
@@ -2695,16 +2699,16 @@
         <v>46</v>
       </c>
       <c r="B23" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D23" s="12" t="s">
+      <c r="E23" s="13" t="s">
         <v>105</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>106</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>49</v>
@@ -2736,16 +2740,16 @@
         <v>15</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="17" t="s">
         <v>108</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>109</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>19</v>
@@ -2777,16 +2781,16 @@
         <v>32</v>
       </c>
       <c r="B25" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D25" s="12" t="s">
+      <c r="E25" s="13" t="s">
         <v>111</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>112</v>
       </c>
       <c r="F25" s="13" t="s">
         <v>35</v>
@@ -2818,22 +2822,22 @@
         <v>46</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="17" t="s">
         <v>114</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>115</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>21</v>
@@ -2859,16 +2863,16 @@
         <v>32</v>
       </c>
       <c r="B27" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C27" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D27" s="12" t="s">
+      <c r="E27" s="13" t="s">
         <v>118</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>119</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>45</v>
@@ -2897,22 +2901,22 @@
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="E28" s="17" t="s">
-        <v>122</v>
-      </c>
       <c r="F28" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G28" s="19"/>
       <c r="H28" s="7" t="s">
@@ -2939,18 +2943,18 @@
         <v>15</v>
       </c>
       <c r="B29" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="D29" s="12" t="s">
+      <c r="E29" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="F29" s="20"/>
+      <c r="F29" s="22"/>
       <c r="G29" s="13" t="s">
         <v>50</v>
       </c>
@@ -2978,16 +2982,16 @@
         <v>15</v>
       </c>
       <c r="B30" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D30" s="5" t="s">
+      <c r="E30" s="17" t="s">
         <v>127</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>128</v>
       </c>
       <c r="F30" s="17" t="s">
         <v>19</v>
@@ -3019,16 +3023,16 @@
         <v>26</v>
       </c>
       <c r="B31" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="D31" s="12" t="s">
+      <c r="E31" s="13" t="s">
         <v>130</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>131</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>57</v>
@@ -3057,19 +3061,19 @@
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="17" t="s">
         <v>133</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>134</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>41</v>
@@ -3098,19 +3102,19 @@
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B33" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C33" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="D33" s="12" t="s">
+      <c r="E33" s="13" t="s">
         <v>136</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>137</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>41</v>
@@ -3142,16 +3146,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D34" s="5" t="s">
+      <c r="E34" s="17" t="s">
         <v>139</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>140</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>67</v>
@@ -3183,18 +3187,18 @@
         <v>46</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D35" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E35" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="E35" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="F35" s="20"/>
+      <c r="F35" s="22"/>
       <c r="G35" s="13" t="s">
         <v>20</v>
       </c>
@@ -3222,16 +3226,16 @@
         <v>26</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D36" s="5" t="s">
+      <c r="E36" s="17" t="s">
         <v>144</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>145</v>
       </c>
       <c r="F36" s="19"/>
       <c r="G36" s="17" t="s">
@@ -3261,16 +3265,16 @@
         <v>46</v>
       </c>
       <c r="B37" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D37" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D37" s="12" t="s">
+      <c r="E37" s="13" t="s">
         <v>147</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>148</v>
       </c>
       <c r="F37" s="13" t="s">
         <v>49</v>
@@ -3302,16 +3306,16 @@
         <v>32</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D38" s="5" t="s">
+      <c r="E38" s="17" t="s">
         <v>150</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>151</v>
       </c>
       <c r="F38" s="17" t="s">
         <v>45</v>
@@ -3343,16 +3347,16 @@
         <v>46</v>
       </c>
       <c r="B39" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D39" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="C39" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="D39" s="12" t="s">
+      <c r="E39" s="13" t="s">
         <v>153</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>154</v>
       </c>
       <c r="F39" s="13" t="s">
         <v>49</v>
@@ -3384,16 +3388,16 @@
         <v>15</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D40" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D40" s="5" t="s">
+      <c r="E40" s="17" t="s">
         <v>156</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>157</v>
       </c>
       <c r="F40" s="17" t="s">
         <v>19</v>
@@ -3425,16 +3429,16 @@
         <v>26</v>
       </c>
       <c r="B41" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="D41" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="C41" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="D41" s="12" t="s">
+      <c r="E41" s="13" t="s">
         <v>159</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>160</v>
       </c>
       <c r="F41" s="13" t="s">
         <v>30</v>
@@ -3463,19 +3467,19 @@
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B42" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D42" s="5" t="s">
+      <c r="E42" s="17" t="s">
         <v>162</v>
-      </c>
-      <c r="E42" s="17" t="s">
-        <v>163</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>41</v>
@@ -3504,24 +3508,24 @@
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B43" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D43" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="C43" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="D43" s="12" t="s">
+      <c r="E43" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="E43" s="13" t="s">
-        <v>166</v>
-      </c>
       <c r="F43" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="G43" s="20"/>
+        <v>87</v>
+      </c>
+      <c r="G43" s="22"/>
       <c r="H43" s="7" t="s">
         <v>21</v>
       </c>
@@ -3546,16 +3550,16 @@
         <v>15</v>
       </c>
       <c r="B44" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D44" s="5" t="s">
+      <c r="E44" s="17" t="s">
         <v>168</v>
-      </c>
-      <c r="E44" s="17" t="s">
-        <v>169</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>19</v>
@@ -3587,16 +3591,16 @@
         <v>15</v>
       </c>
       <c r="B45" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D45" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="C45" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="D45" s="12" t="s">
+      <c r="E45" s="13" t="s">
         <v>171</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>172</v>
       </c>
       <c r="F45" s="13" t="s">
         <v>49</v>
@@ -3628,16 +3632,16 @@
         <v>26</v>
       </c>
       <c r="B46" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D46" s="5" t="s">
+      <c r="E46" s="17" t="s">
         <v>174</v>
-      </c>
-      <c r="E46" s="17" t="s">
-        <v>175</v>
       </c>
       <c r="F46" s="17" t="s">
         <v>57</v>
@@ -3666,24 +3670,24 @@
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B47" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="D47" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="C47" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="D47" s="12" t="s">
+      <c r="E47" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="E47" s="13" t="s">
-        <v>178</v>
-      </c>
       <c r="F47" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="G47" s="20"/>
+        <v>87</v>
+      </c>
+      <c r="G47" s="22"/>
       <c r="H47" s="7" t="s">
         <v>21</v>
       </c>
@@ -3708,16 +3712,16 @@
         <v>15</v>
       </c>
       <c r="B48" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D48" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D48" s="5" t="s">
+      <c r="E48" s="17" t="s">
         <v>180</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>181</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>49</v>
@@ -3749,21 +3753,21 @@
         <v>37</v>
       </c>
       <c r="B49" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D49" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="C49" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="D49" s="12" t="s">
+      <c r="E49" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="E49" s="13" t="s">
-        <v>184</v>
-      </c>
       <c r="F49" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G49" s="20"/>
+        <v>99</v>
+      </c>
+      <c r="G49" s="22"/>
       <c r="H49" s="7" t="s">
         <v>21</v>
       </c>
@@ -3788,22 +3792,22 @@
         <v>37</v>
       </c>
       <c r="B50" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D50" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D50" s="5" t="s">
+      <c r="E50" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="E50" s="17" t="s">
-        <v>187</v>
-      </c>
       <c r="F50" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>21</v>
@@ -3813,8 +3817,8 @@
       </c>
       <c r="J50" s="14"/>
       <c r="K50" s="14"/>
-      <c r="L50" s="21" t="s">
-        <v>188</v>
+      <c r="L50" s="23" t="s">
+        <v>187</v>
       </c>
       <c r="M50" s="9" t="s">
         <v>23</v>
@@ -3831,16 +3835,16 @@
         <v>32</v>
       </c>
       <c r="B51" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="C51" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="D51" s="12" t="s">
+      <c r="E51" s="13" t="s">
         <v>190</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>191</v>
       </c>
       <c r="F51" s="13" t="s">
         <v>35</v>
@@ -3872,16 +3876,16 @@
         <v>26</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D52" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E52" s="17" t="s">
         <v>192</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>193</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>57</v>
@@ -3913,16 +3917,16 @@
         <v>46</v>
       </c>
       <c r="B53" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="D53" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="C53" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="D53" s="12" t="s">
+      <c r="E53" s="13" t="s">
         <v>195</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>196</v>
       </c>
       <c r="F53" s="13" t="s">
         <v>49</v>
@@ -3954,19 +3958,19 @@
         <v>37</v>
       </c>
       <c r="B54" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D54" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D54" s="5" t="s">
+      <c r="E54" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="E54" s="17" t="s">
-        <v>199</v>
-      </c>
       <c r="F54" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G54" s="19"/>
       <c r="H54" s="7" t="s">
@@ -3993,16 +3997,16 @@
         <v>26</v>
       </c>
       <c r="B55" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="D55" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="C55" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="D55" s="12" t="s">
+      <c r="E55" s="13" t="s">
         <v>201</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>202</v>
       </c>
       <c r="F55" s="13" t="s">
         <v>30</v>
@@ -4034,16 +4038,16 @@
         <v>32</v>
       </c>
       <c r="B56" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D56" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D56" s="5" t="s">
+      <c r="E56" s="17" t="s">
         <v>204</v>
-      </c>
-      <c r="E56" s="17" t="s">
-        <v>205</v>
       </c>
       <c r="F56" s="17" t="s">
         <v>35</v>
@@ -4075,21 +4079,21 @@
         <v>37</v>
       </c>
       <c r="B57" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="D57" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="C57" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="D57" s="12" t="s">
+      <c r="E57" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="E57" s="13" t="s">
-        <v>208</v>
-      </c>
       <c r="F57" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G57" s="20"/>
+        <v>99</v>
+      </c>
+      <c r="G57" s="22"/>
       <c r="H57" s="7" t="s">
         <v>21</v>
       </c>
@@ -4114,16 +4118,16 @@
         <v>26</v>
       </c>
       <c r="B58" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D58" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="D58" s="5" t="s">
+      <c r="E58" s="17" t="s">
         <v>210</v>
-      </c>
-      <c r="E58" s="17" t="s">
-        <v>211</v>
       </c>
       <c r="F58" s="17" t="s">
         <v>57</v>
@@ -4155,21 +4159,23 @@
         <v>46</v>
       </c>
       <c r="B59" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="D59" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="C59" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="D59" s="12" t="s">
+      <c r="E59" s="13" t="s">
         <v>213</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>214</v>
       </c>
       <c r="F59" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G59" s="20"/>
+      <c r="G59" s="24" t="s">
+        <v>50</v>
+      </c>
       <c r="H59" s="7" t="s">
         <v>21</v>
       </c>
@@ -4194,16 +4200,16 @@
         <v>15</v>
       </c>
       <c r="B60" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D60" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D60" s="5" t="s">
+      <c r="E60" s="17" t="s">
         <v>216</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>217</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>19</v>
@@ -4235,16 +4241,16 @@
         <v>26</v>
       </c>
       <c r="B61" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D61" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="C61" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="D61" s="12" t="s">
+      <c r="E61" s="13" t="s">
         <v>219</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>220</v>
       </c>
       <c r="F61" s="13" t="s">
         <v>30</v>
@@ -4276,16 +4282,16 @@
         <v>32</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D62" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E62" s="17" t="s">
         <v>221</v>
-      </c>
-      <c r="E62" s="17" t="s">
-        <v>222</v>
       </c>
       <c r="F62" s="17" t="s">
         <v>35</v>
@@ -4317,16 +4323,16 @@
         <v>15</v>
       </c>
       <c r="B63" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D63" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="C63" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="D63" s="12" t="s">
+      <c r="E63" s="13" t="s">
         <v>224</v>
-      </c>
-      <c r="E63" s="13" t="s">
-        <v>225</v>
       </c>
       <c r="F63" s="13" t="s">
         <v>49</v>
@@ -4358,16 +4364,16 @@
         <v>26</v>
       </c>
       <c r="B64" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D64" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D64" s="5" t="s">
+      <c r="E64" s="17" t="s">
         <v>227</v>
-      </c>
-      <c r="E64" s="17" t="s">
-        <v>228</v>
       </c>
       <c r="F64" s="17" t="s">
         <v>57</v>
@@ -4399,16 +4405,16 @@
         <v>32</v>
       </c>
       <c r="B65" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D65" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="C65" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="D65" s="12" t="s">
+      <c r="E65" s="13" t="s">
         <v>230</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>231</v>
       </c>
       <c r="F65" s="13" t="s">
         <v>35</v>
@@ -4437,19 +4443,19 @@
     </row>
     <row r="66" ht="12.75" customHeight="1">
       <c r="A66" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D66" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="D66" s="5" t="s">
+      <c r="E66" s="17" t="s">
         <v>233</v>
-      </c>
-      <c r="E66" s="17" t="s">
-        <v>234</v>
       </c>
       <c r="F66" s="17" t="s">
         <v>41</v>
@@ -4481,16 +4487,16 @@
         <v>46</v>
       </c>
       <c r="B67" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D67" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="C67" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="D67" s="12" t="s">
+      <c r="E67" s="13" t="s">
         <v>236</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>237</v>
       </c>
       <c r="F67" s="13" t="s">
         <v>49</v>
@@ -4519,19 +4525,19 @@
     </row>
     <row r="68" ht="12.75" customHeight="1">
       <c r="A68" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B68" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D68" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="D68" s="5" t="s">
+      <c r="E68" s="17" t="s">
         <v>239</v>
-      </c>
-      <c r="E68" s="17" t="s">
-        <v>240</v>
       </c>
       <c r="F68" s="17" t="s">
         <v>41</v>
@@ -4560,25 +4566,25 @@
     </row>
     <row r="69" ht="12.75" customHeight="1">
       <c r="A69" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B69" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="C69" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="D69" s="12" t="s">
+      <c r="E69" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="E69" s="13" t="s">
+      <c r="F69" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="G69" s="13" t="s">
         <v>243</v>
-      </c>
-      <c r="F69" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="G69" s="13" t="s">
-        <v>244</v>
       </c>
       <c r="H69" s="7" t="s">
         <v>21</v>
@@ -4604,16 +4610,16 @@
         <v>15</v>
       </c>
       <c r="B70" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D70" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D70" s="5" t="s">
+      <c r="E70" s="17" t="s">
         <v>246</v>
-      </c>
-      <c r="E70" s="17" t="s">
-        <v>247</v>
       </c>
       <c r="F70" s="19"/>
       <c r="G70" s="17" t="s">
@@ -4643,21 +4649,21 @@
         <v>37</v>
       </c>
       <c r="B71" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D71" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="C71" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D71" s="12" t="s">
+      <c r="E71" s="13" t="s">
         <v>249</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>250</v>
       </c>
       <c r="F71" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G71" s="20"/>
+      <c r="G71" s="22"/>
       <c r="H71" s="7" t="s">
         <v>21</v>
       </c>
@@ -4682,16 +4688,16 @@
         <v>15</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D72" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="E72" s="17" t="s">
         <v>251</v>
-      </c>
-      <c r="E72" s="17" t="s">
-        <v>252</v>
       </c>
       <c r="F72" s="17" t="s">
         <v>49</v>
@@ -4720,25 +4726,25 @@
     </row>
     <row r="73" ht="12.75" customHeight="1">
       <c r="A73" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B73" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="D73" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="C73" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="D73" s="12" t="s">
+      <c r="E73" s="13" t="s">
         <v>254</v>
-      </c>
-      <c r="E73" s="13" t="s">
-        <v>255</v>
       </c>
       <c r="F73" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G73" s="13" t="s">
-        <v>63</v>
+      <c r="G73" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="H73" s="7" t="s">
         <v>21</v>
@@ -4761,22 +4767,22 @@
     </row>
     <row r="74" ht="12.75" customHeight="1">
       <c r="A74" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B74" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D74" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D74" s="5" t="s">
+      <c r="E74" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="E74" s="17" t="s">
-        <v>258</v>
-      </c>
       <c r="F74" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G74" s="19"/>
       <c r="H74" s="7" t="s">
@@ -4800,19 +4806,19 @@
     </row>
     <row r="75" ht="12.75" customHeight="1">
       <c r="A75" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B75" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="D75" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="C75" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="D75" s="12" t="s">
+      <c r="E75" s="13" t="s">
         <v>260</v>
-      </c>
-      <c r="E75" s="13" t="s">
-        <v>261</v>
       </c>
       <c r="F75" s="13" t="s">
         <v>41</v>
@@ -4841,22 +4847,22 @@
     </row>
     <row r="76" ht="12.75" customHeight="1">
       <c r="A76" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B76" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D76" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="D76" s="5" t="s">
+      <c r="E76" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="E76" s="17" t="s">
+      <c r="F76" s="17" t="s">
         <v>264</v>
-      </c>
-      <c r="F76" s="17" t="s">
-        <v>265</v>
       </c>
       <c r="G76" s="19"/>
       <c r="H76" s="7" t="s">
@@ -4883,16 +4889,16 @@
         <v>15</v>
       </c>
       <c r="B77" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D77" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="C77" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="D77" s="12" t="s">
+      <c r="E77" s="13" t="s">
         <v>267</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>268</v>
       </c>
       <c r="F77" s="13" t="s">
         <v>19</v>
@@ -4921,19 +4927,19 @@
     </row>
     <row r="78" ht="12.75" customHeight="1">
       <c r="A78" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B78" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="D78" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="C78" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D78" s="5" t="s">
+      <c r="E78" s="17" t="s">
         <v>270</v>
-      </c>
-      <c r="E78" s="17" t="s">
-        <v>271</v>
       </c>
       <c r="F78" s="17" t="s">
         <v>41</v>
@@ -4965,22 +4971,22 @@
         <v>32</v>
       </c>
       <c r="B79" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D79" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="C79" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="D79" s="12" t="s">
+      <c r="E79" s="13" t="s">
         <v>273</v>
-      </c>
-      <c r="E79" s="13" t="s">
-        <v>274</v>
       </c>
       <c r="F79" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G79" s="13" t="s">
-        <v>63</v>
+      <c r="G79" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="H79" s="7" t="s">
         <v>21</v>
@@ -5006,19 +5012,19 @@
         <v>37</v>
       </c>
       <c r="B80" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D80" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C80" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D80" s="5" t="s">
+      <c r="E80" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="E80" s="17" t="s">
-        <v>277</v>
-      </c>
       <c r="F80" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G80" s="19"/>
       <c r="H80" s="7" t="s">
@@ -5045,16 +5051,16 @@
         <v>26</v>
       </c>
       <c r="B81" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D81" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="C81" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="D81" s="12" t="s">
+      <c r="E81" s="13" t="s">
         <v>279</v>
-      </c>
-      <c r="E81" s="13" t="s">
-        <v>280</v>
       </c>
       <c r="F81" s="13" t="s">
         <v>57</v>
@@ -5086,22 +5092,22 @@
         <v>32</v>
       </c>
       <c r="B82" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D82" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="C82" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="D82" s="5" t="s">
+      <c r="E82" s="17" t="s">
         <v>282</v>
-      </c>
-      <c r="E82" s="17" t="s">
-        <v>283</v>
       </c>
       <c r="F82" s="17" t="s">
         <v>45</v>
       </c>
       <c r="G82" s="17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H82" s="7" t="s">
         <v>21</v>
@@ -5111,11 +5117,11 @@
       </c>
       <c r="J82" s="14"/>
       <c r="K82" s="14"/>
-      <c r="L82" s="21" t="s">
-        <v>188</v>
+      <c r="L82" s="23" t="s">
+        <v>187</v>
       </c>
       <c r="M82" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N82" s="7" t="b">
         <v>1</v>
@@ -5129,16 +5135,16 @@
         <v>15</v>
       </c>
       <c r="B83" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D83" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="C83" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="D83" s="12" t="s">
+      <c r="E83" s="13" t="s">
         <v>286</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>287</v>
       </c>
       <c r="F83" s="13" t="s">
         <v>19</v>
@@ -5156,7 +5162,7 @@
       <c r="K83" s="14"/>
       <c r="L83" s="15"/>
       <c r="M83" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N83" s="7" t="b">
         <v>1</v>
@@ -5170,16 +5176,16 @@
         <v>15</v>
       </c>
       <c r="B84" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D84" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="C84" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="D84" s="5" t="s">
+      <c r="E84" s="17" t="s">
         <v>289</v>
-      </c>
-      <c r="E84" s="17" t="s">
-        <v>290</v>
       </c>
       <c r="F84" s="17" t="s">
         <v>49</v>
@@ -5197,7 +5203,7 @@
       <c r="K84" s="14"/>
       <c r="L84" s="18"/>
       <c r="M84" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N84" s="7" t="b">
         <v>1</v>
@@ -5211,16 +5217,16 @@
         <v>15</v>
       </c>
       <c r="B85" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C85" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="D85" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="E85" s="13" t="s">
         <v>293</v>
-      </c>
-      <c r="E85" s="13" t="s">
-        <v>294</v>
       </c>
       <c r="F85" s="13" t="s">
         <v>19</v>
@@ -5238,7 +5244,7 @@
       <c r="K85" s="14"/>
       <c r="L85" s="15"/>
       <c r="M85" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N85" s="7" t="b">
         <v>1</v>
@@ -5252,19 +5258,19 @@
         <v>37</v>
       </c>
       <c r="B86" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D86" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="C86" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="D86" s="5" t="s">
+      <c r="E86" s="17" t="s">
         <v>296</v>
       </c>
-      <c r="E86" s="17" t="s">
-        <v>297</v>
-      </c>
       <c r="F86" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G86" s="19"/>
       <c r="H86" s="7" t="s">
@@ -5277,7 +5283,7 @@
       <c r="K86" s="14"/>
       <c r="L86" s="18"/>
       <c r="M86" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N86" s="7" t="b">
         <v>1</v>
@@ -5291,21 +5297,21 @@
         <v>37</v>
       </c>
       <c r="B87" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="D87" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="C87" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="D87" s="12" t="s">
+      <c r="E87" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="E87" s="13" t="s">
-        <v>300</v>
-      </c>
       <c r="F87" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="G87" s="20"/>
+        <v>79</v>
+      </c>
+      <c r="G87" s="22"/>
       <c r="H87" s="7" t="s">
         <v>21</v>
       </c>
@@ -5316,7 +5322,7 @@
       <c r="K87" s="14"/>
       <c r="L87" s="15"/>
       <c r="M87" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N87" s="7" t="b">
         <v>1</v>
@@ -5330,16 +5336,16 @@
         <v>32</v>
       </c>
       <c r="B88" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D88" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="C88" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="D88" s="5" t="s">
+      <c r="E88" s="17" t="s">
         <v>302</v>
-      </c>
-      <c r="E88" s="17" t="s">
-        <v>303</v>
       </c>
       <c r="F88" s="17" t="s">
         <v>45</v>
@@ -5357,7 +5363,7 @@
       <c r="K88" s="14"/>
       <c r="L88" s="18"/>
       <c r="M88" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N88" s="7" t="b">
         <v>1</v>
@@ -5371,16 +5377,16 @@
         <v>46</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D89" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="E89" s="13" t="s">
         <v>304</v>
-      </c>
-      <c r="E89" s="13" t="s">
-        <v>305</v>
       </c>
       <c r="F89" s="13" t="s">
         <v>62</v>
@@ -5398,7 +5404,7 @@
       <c r="K89" s="14"/>
       <c r="L89" s="15"/>
       <c r="M89" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N89" s="7" t="b">
         <v>1</v>
@@ -5412,16 +5418,16 @@
         <v>26</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D90" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="E90" s="17" t="s">
         <v>306</v>
-      </c>
-      <c r="E90" s="17" t="s">
-        <v>307</v>
       </c>
       <c r="F90" s="17" t="s">
         <v>30</v>
@@ -5439,7 +5445,7 @@
       <c r="K90" s="14"/>
       <c r="L90" s="18"/>
       <c r="M90" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N90" s="7" t="b">
         <v>1</v>
@@ -5453,18 +5459,18 @@
         <v>46</v>
       </c>
       <c r="B91" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="D91" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="C91" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="D91" s="12" t="s">
+      <c r="E91" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="E91" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="F91" s="20"/>
+      <c r="F91" s="22"/>
       <c r="G91" s="13" t="s">
         <v>63</v>
       </c>
@@ -5478,7 +5484,7 @@
       <c r="K91" s="14"/>
       <c r="L91" s="15"/>
       <c r="M91" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N91" s="7" t="b">
         <v>1</v>
@@ -5492,22 +5498,22 @@
         <v>37</v>
       </c>
       <c r="B92" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D92" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="C92" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="D92" s="5" t="s">
+      <c r="E92" s="17" t="s">
         <v>312</v>
       </c>
-      <c r="E92" s="17" t="s">
-        <v>313</v>
-      </c>
       <c r="F92" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G92" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H92" s="7" t="s">
         <v>21</v>
@@ -5517,11 +5523,11 @@
       </c>
       <c r="J92" s="14"/>
       <c r="K92" s="14"/>
-      <c r="L92" s="21" t="s">
-        <v>188</v>
+      <c r="L92" s="23" t="s">
+        <v>187</v>
       </c>
       <c r="M92" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N92" s="7" t="b">
         <v>1</v>
@@ -5535,16 +5541,16 @@
         <v>32</v>
       </c>
       <c r="B93" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="D93" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="C93" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="D93" s="12" t="s">
+      <c r="E93" s="13" t="s">
         <v>315</v>
-      </c>
-      <c r="E93" s="13" t="s">
-        <v>316</v>
       </c>
       <c r="F93" s="13" t="s">
         <v>45</v>
@@ -5562,7 +5568,7 @@
       <c r="K93" s="14"/>
       <c r="L93" s="15"/>
       <c r="M93" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N93" s="7" t="b">
         <v>1</v>
@@ -5576,16 +5582,16 @@
         <v>46</v>
       </c>
       <c r="B94" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="D94" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="C94" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="D94" s="5" t="s">
+      <c r="E94" s="17" t="s">
         <v>318</v>
-      </c>
-      <c r="E94" s="17" t="s">
-        <v>319</v>
       </c>
       <c r="F94" s="17" t="s">
         <v>49</v>
@@ -5603,7 +5609,7 @@
       <c r="K94" s="14"/>
       <c r="L94" s="18"/>
       <c r="M94" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N94" s="7" t="b">
         <v>1</v>
@@ -5617,23 +5623,21 @@
         <v>37</v>
       </c>
       <c r="B95" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="D95" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="C95" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="D95" s="12" t="s">
+      <c r="E95" s="13" t="s">
         <v>321</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>322</v>
       </c>
       <c r="F95" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G95" s="13" t="s">
-        <v>50</v>
-      </c>
+      <c r="G95" s="13"/>
       <c r="H95" s="7" t="s">
         <v>21</v>
       </c>
@@ -5644,7 +5648,7 @@
       <c r="K95" s="14"/>
       <c r="L95" s="15"/>
       <c r="M95" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N95" s="7" t="b">
         <v>1</v>
@@ -5658,16 +5662,16 @@
         <v>15</v>
       </c>
       <c r="B96" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="D96" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="C96" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="D96" s="5" t="s">
+      <c r="E96" s="17" t="s">
         <v>324</v>
-      </c>
-      <c r="E96" s="17" t="s">
-        <v>325</v>
       </c>
       <c r="F96" s="17" t="s">
         <v>49</v>
@@ -5685,7 +5689,7 @@
       <c r="K96" s="14"/>
       <c r="L96" s="18"/>
       <c r="M96" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N96" s="7" t="b">
         <v>1</v>
@@ -5696,19 +5700,19 @@
     </row>
     <row r="97" ht="12.75" customHeight="1">
       <c r="A97" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B97" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="D97" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="C97" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="D97" s="12" t="s">
+      <c r="E97" s="13" t="s">
         <v>327</v>
-      </c>
-      <c r="E97" s="13" t="s">
-        <v>328</v>
       </c>
       <c r="F97" s="13" t="s">
         <v>41</v>
@@ -5726,7 +5730,7 @@
       <c r="K97" s="14"/>
       <c r="L97" s="15"/>
       <c r="M97" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N97" s="7" t="b">
         <v>1</v>
@@ -5740,16 +5744,16 @@
         <v>15</v>
       </c>
       <c r="B98" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="D98" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="C98" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="D98" s="5" t="s">
+      <c r="E98" s="17" t="s">
         <v>330</v>
-      </c>
-      <c r="E98" s="17" t="s">
-        <v>331</v>
       </c>
       <c r="F98" s="17" t="s">
         <v>49</v>
@@ -5767,7 +5771,7 @@
       <c r="K98" s="14"/>
       <c r="L98" s="18"/>
       <c r="M98" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N98" s="7" t="b">
         <v>1</v>
@@ -5781,16 +5785,16 @@
         <v>15</v>
       </c>
       <c r="B99" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="D99" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="C99" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="D99" s="12" t="s">
+      <c r="E99" s="13" t="s">
         <v>333</v>
-      </c>
-      <c r="E99" s="13" t="s">
-        <v>334</v>
       </c>
       <c r="F99" s="13" t="s">
         <v>49</v>
@@ -5808,7 +5812,7 @@
       <c r="K99" s="14"/>
       <c r="L99" s="15"/>
       <c r="M99" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N99" s="7" t="b">
         <v>1</v>
@@ -5822,16 +5826,16 @@
         <v>26</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D100" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="E100" s="17" t="s">
         <v>335</v>
-      </c>
-      <c r="E100" s="17" t="s">
-        <v>336</v>
       </c>
       <c r="F100" s="17" t="s">
         <v>30</v>
@@ -5849,7 +5853,7 @@
       <c r="K100" s="14"/>
       <c r="L100" s="18"/>
       <c r="M100" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N100" s="7" t="b">
         <v>1</v>
@@ -5860,24 +5864,24 @@
     </row>
     <row r="101" ht="12.75" customHeight="1">
       <c r="A101" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B101" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D101" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="C101" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="D101" s="12" t="s">
+      <c r="E101" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="E101" s="13" t="s">
-        <v>339</v>
-      </c>
       <c r="F101" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="G101" s="20"/>
+        <v>87</v>
+      </c>
+      <c r="G101" s="22"/>
       <c r="H101" s="7" t="s">
         <v>21</v>
       </c>
@@ -5888,7 +5892,7 @@
       <c r="K101" s="14"/>
       <c r="L101" s="15"/>
       <c r="M101" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N101" s="7" t="b">
         <v>1</v>
@@ -5902,16 +5906,16 @@
         <v>15</v>
       </c>
       <c r="B102" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D102" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="C102" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="D102" s="5" t="s">
+      <c r="E102" s="17" t="s">
         <v>341</v>
-      </c>
-      <c r="E102" s="17" t="s">
-        <v>342</v>
       </c>
       <c r="F102" s="17" t="s">
         <v>49</v>
@@ -5929,7 +5933,7 @@
       <c r="K102" s="14"/>
       <c r="L102" s="18"/>
       <c r="M102" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N102" s="7" t="b">
         <v>1</v>
@@ -5943,16 +5947,16 @@
         <v>26</v>
       </c>
       <c r="B103" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="D103" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="C103" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="D103" s="12" t="s">
+      <c r="E103" s="13" t="s">
         <v>344</v>
-      </c>
-      <c r="E103" s="13" t="s">
-        <v>345</v>
       </c>
       <c r="F103" s="13" t="s">
         <v>30</v>
@@ -5970,7 +5974,7 @@
       <c r="K103" s="14"/>
       <c r="L103" s="15"/>
       <c r="M103" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N103" s="7" t="b">
         <v>1</v>
@@ -5984,16 +5988,16 @@
         <v>32</v>
       </c>
       <c r="B104" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="D104" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="C104" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="D104" s="5" t="s">
+      <c r="E104" s="17" t="s">
         <v>347</v>
-      </c>
-      <c r="E104" s="17" t="s">
-        <v>348</v>
       </c>
       <c r="F104" s="17" t="s">
         <v>35</v>
@@ -6011,7 +6015,7 @@
       <c r="K104" s="14"/>
       <c r="L104" s="18"/>
       <c r="M104" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N104" s="7" t="b">
         <v>1</v>
@@ -6025,16 +6029,16 @@
         <v>46</v>
       </c>
       <c r="B105" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="D105" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="C105" s="12" t="s">
-        <v>349</v>
-      </c>
-      <c r="D105" s="12" t="s">
+      <c r="E105" s="13" t="s">
         <v>350</v>
-      </c>
-      <c r="E105" s="13" t="s">
-        <v>351</v>
       </c>
       <c r="F105" s="13" t="s">
         <v>49</v>
@@ -6052,7 +6056,7 @@
       <c r="K105" s="14"/>
       <c r="L105" s="15"/>
       <c r="M105" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N105" s="7" t="b">
         <v>1</v>
@@ -6066,16 +6070,16 @@
         <v>26</v>
       </c>
       <c r="B106" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D106" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="C106" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="D106" s="5" t="s">
+      <c r="E106" s="17" t="s">
         <v>353</v>
-      </c>
-      <c r="E106" s="17" t="s">
-        <v>354</v>
       </c>
       <c r="F106" s="17" t="s">
         <v>57</v>
@@ -6093,7 +6097,7 @@
       <c r="K106" s="14"/>
       <c r="L106" s="18"/>
       <c r="M106" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N106" s="7" t="b">
         <v>1</v>
@@ -6104,24 +6108,24 @@
     </row>
     <row r="107" ht="12.75" customHeight="1">
       <c r="A107" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B107" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D107" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="C107" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="D107" s="12" t="s">
+      <c r="E107" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="E107" s="13" t="s">
-        <v>357</v>
-      </c>
       <c r="F107" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="G107" s="20"/>
+        <v>87</v>
+      </c>
+      <c r="G107" s="22"/>
       <c r="H107" s="7" t="s">
         <v>21</v>
       </c>
@@ -6132,7 +6136,7 @@
       <c r="K107" s="14"/>
       <c r="L107" s="15"/>
       <c r="M107" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N107" s="7" t="b">
         <v>1</v>
@@ -6146,16 +6150,16 @@
         <v>15</v>
       </c>
       <c r="B108" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D108" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="C108" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D108" s="5" t="s">
+      <c r="E108" s="17" t="s">
         <v>359</v>
-      </c>
-      <c r="E108" s="17" t="s">
-        <v>360</v>
       </c>
       <c r="F108" s="19"/>
       <c r="G108" s="17" t="s">
@@ -6171,7 +6175,7 @@
       <c r="K108" s="14"/>
       <c r="L108" s="18"/>
       <c r="M108" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N108" s="7" t="b">
         <v>1</v>
@@ -6185,22 +6189,22 @@
         <v>26</v>
       </c>
       <c r="B109" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D109" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C109" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="D109" s="12" t="s">
+      <c r="E109" s="13" t="s">
         <v>362</v>
-      </c>
-      <c r="E109" s="13" t="s">
-        <v>363</v>
       </c>
       <c r="F109" s="13" t="s">
         <v>57</v>
       </c>
       <c r="G109" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H109" s="7" t="s">
         <v>21</v>
@@ -6212,7 +6216,7 @@
       <c r="K109" s="14"/>
       <c r="L109" s="15"/>
       <c r="M109" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N109" s="7" t="b">
         <v>1</v>
@@ -6226,16 +6230,16 @@
         <v>15</v>
       </c>
       <c r="B110" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="D110" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="C110" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="D110" s="5" t="s">
+      <c r="E110" s="17" t="s">
         <v>365</v>
-      </c>
-      <c r="E110" s="17" t="s">
-        <v>366</v>
       </c>
       <c r="F110" s="17" t="s">
         <v>49</v>
@@ -6253,7 +6257,7 @@
       <c r="K110" s="14"/>
       <c r="L110" s="18"/>
       <c r="M110" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N110" s="7" t="b">
         <v>1</v>
@@ -6267,16 +6271,16 @@
         <v>15</v>
       </c>
       <c r="B111" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D111" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="D111" s="12" t="s">
+      <c r="E111" s="13" t="s">
         <v>368</v>
-      </c>
-      <c r="E111" s="13" t="s">
-        <v>369</v>
       </c>
       <c r="F111" s="13" t="s">
         <v>49</v>
@@ -6294,7 +6298,7 @@
       <c r="K111" s="14"/>
       <c r="L111" s="15"/>
       <c r="M111" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N111" s="7" t="b">
         <v>1</v>
@@ -6308,16 +6312,16 @@
         <v>26</v>
       </c>
       <c r="B112" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D112" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="C112" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="D112" s="5" t="s">
+      <c r="E112" s="17" t="s">
         <v>371</v>
-      </c>
-      <c r="E112" s="17" t="s">
-        <v>372</v>
       </c>
       <c r="F112" s="17" t="s">
         <v>57</v>
@@ -6335,7 +6339,7 @@
       <c r="K112" s="14"/>
       <c r="L112" s="18"/>
       <c r="M112" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N112" s="7" t="b">
         <v>1</v>
@@ -6349,22 +6353,22 @@
         <v>46</v>
       </c>
       <c r="B113" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="D113" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="C113" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="D113" s="12" t="s">
+      <c r="E113" s="13" t="s">
         <v>374</v>
-      </c>
-      <c r="E113" s="13" t="s">
-        <v>375</v>
       </c>
       <c r="F113" s="13" t="s">
         <v>49</v>
       </c>
       <c r="G113" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H113" s="7" t="s">
         <v>21</v>
@@ -6376,7 +6380,7 @@
       <c r="K113" s="14"/>
       <c r="L113" s="15"/>
       <c r="M113" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N113" s="7" t="b">
         <v>1</v>
@@ -6390,16 +6394,16 @@
         <v>32</v>
       </c>
       <c r="B114" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="D114" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="C114" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="D114" s="5" t="s">
+      <c r="E114" s="17" t="s">
         <v>377</v>
-      </c>
-      <c r="E114" s="17" t="s">
-        <v>378</v>
       </c>
       <c r="F114" s="17" t="s">
         <v>45</v>
@@ -6417,7 +6421,7 @@
       <c r="K114" s="14"/>
       <c r="L114" s="18"/>
       <c r="M114" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N114" s="7" t="b">
         <v>1</v>
@@ -6431,16 +6435,16 @@
         <v>46</v>
       </c>
       <c r="B115" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="D115" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="C115" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="D115" s="12" t="s">
+      <c r="E115" s="13" t="s">
         <v>380</v>
-      </c>
-      <c r="E115" s="13" t="s">
-        <v>381</v>
       </c>
       <c r="F115" s="13" t="s">
         <v>49</v>
@@ -6458,7 +6462,7 @@
       <c r="K115" s="14"/>
       <c r="L115" s="15"/>
       <c r="M115" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N115" s="7" t="b">
         <v>1</v>
@@ -6472,16 +6476,16 @@
         <v>32</v>
       </c>
       <c r="B116" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="D116" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="C116" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="D116" s="5" t="s">
+      <c r="E116" s="17" t="s">
         <v>383</v>
-      </c>
-      <c r="E116" s="17" t="s">
-        <v>384</v>
       </c>
       <c r="F116" s="17" t="s">
         <v>45</v>
@@ -6499,7 +6503,7 @@
       <c r="K116" s="14"/>
       <c r="L116" s="18"/>
       <c r="M116" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N116" s="7" t="b">
         <v>1</v>
@@ -6513,18 +6517,18 @@
         <v>15</v>
       </c>
       <c r="B117" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="D117" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="C117" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="D117" s="12" t="s">
+      <c r="E117" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="E117" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="F117" s="20"/>
+      <c r="F117" s="22"/>
       <c r="G117" s="13" t="s">
         <v>50</v>
       </c>
@@ -6538,7 +6542,7 @@
       <c r="K117" s="14"/>
       <c r="L117" s="15"/>
       <c r="M117" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N117" s="7" t="b">
         <v>1</v>
@@ -6552,16 +6556,16 @@
         <v>15</v>
       </c>
       <c r="B118" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="D118" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="C118" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="D118" s="5" t="s">
+      <c r="E118" s="17" t="s">
         <v>389</v>
-      </c>
-      <c r="E118" s="17" t="s">
-        <v>390</v>
       </c>
       <c r="F118" s="17" t="s">
         <v>49</v>
@@ -6579,7 +6583,7 @@
       <c r="K118" s="14"/>
       <c r="L118" s="18"/>
       <c r="M118" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N118" s="7" t="b">
         <v>1</v>
@@ -6593,16 +6597,16 @@
         <v>26</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D119" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="E119" s="13" t="s">
         <v>391</v>
-      </c>
-      <c r="E119" s="13" t="s">
-        <v>392</v>
       </c>
       <c r="F119" s="13" t="s">
         <v>30</v>
@@ -6620,7 +6624,7 @@
       <c r="K119" s="14"/>
       <c r="L119" s="15"/>
       <c r="M119" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N119" s="7" t="b">
         <v>1</v>
@@ -6634,20 +6638,20 @@
         <v>46</v>
       </c>
       <c r="B120" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="D120" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C120" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="D120" s="5" t="s">
+      <c r="E120" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="E120" s="17" t="s">
-        <v>395</v>
-      </c>
       <c r="F120" s="19"/>
-      <c r="G120" s="17" t="s">
-        <v>244</v>
+      <c r="G120" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="H120" s="7" t="s">
         <v>21</v>
@@ -6659,7 +6663,7 @@
       <c r="K120" s="14"/>
       <c r="L120" s="18"/>
       <c r="M120" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N120" s="7" t="b">
         <v>1</v>
@@ -6673,18 +6677,18 @@
         <v>15</v>
       </c>
       <c r="B121" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="D121" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="C121" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="D121" s="12" t="s">
+      <c r="E121" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="E121" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="F121" s="20"/>
+      <c r="F121" s="22"/>
       <c r="G121" s="13" t="s">
         <v>20</v>
       </c>
@@ -6698,7 +6702,7 @@
       <c r="K121" s="14"/>
       <c r="L121" s="15"/>
       <c r="M121" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N121" s="7" t="b">
         <v>1</v>
@@ -6712,16 +6716,16 @@
         <v>32</v>
       </c>
       <c r="B122" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D122" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="C122" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="D122" s="5" t="s">
+      <c r="E122" s="17" t="s">
         <v>400</v>
-      </c>
-      <c r="E122" s="17" t="s">
-        <v>401</v>
       </c>
       <c r="F122" s="17" t="s">
         <v>35</v>
@@ -6739,7 +6743,7 @@
       <c r="K122" s="14"/>
       <c r="L122" s="18"/>
       <c r="M122" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N122" s="7" t="b">
         <v>1</v>
@@ -6753,16 +6757,16 @@
         <v>46</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D123" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="E123" s="13" t="s">
         <v>402</v>
-      </c>
-      <c r="E123" s="13" t="s">
-        <v>403</v>
       </c>
       <c r="F123" s="13" t="s">
         <v>62</v>
@@ -6780,7 +6784,7 @@
       <c r="K123" s="14"/>
       <c r="L123" s="15"/>
       <c r="M123" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N123" s="7" t="b">
         <v>1</v>
@@ -6794,22 +6798,22 @@
         <v>26</v>
       </c>
       <c r="B124" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D124" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="C124" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="D124" s="5" t="s">
+      <c r="E124" s="17" t="s">
         <v>405</v>
-      </c>
-      <c r="E124" s="17" t="s">
-        <v>406</v>
       </c>
       <c r="F124" s="17" t="s">
         <v>57</v>
       </c>
       <c r="G124" s="17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H124" s="7" t="s">
         <v>21</v>
@@ -6821,7 +6825,7 @@
       <c r="K124" s="14"/>
       <c r="L124" s="18"/>
       <c r="M124" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N124" s="7" t="b">
         <v>1</v>
@@ -6835,16 +6839,16 @@
         <v>15</v>
       </c>
       <c r="B125" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="D125" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="C125" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="D125" s="12" t="s">
+      <c r="E125" s="13" t="s">
         <v>408</v>
-      </c>
-      <c r="E125" s="13" t="s">
-        <v>409</v>
       </c>
       <c r="F125" s="13" t="s">
         <v>49</v>
@@ -6862,7 +6866,7 @@
       <c r="K125" s="14"/>
       <c r="L125" s="15"/>
       <c r="M125" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N125" s="7" t="b">
         <v>1</v>
@@ -6873,22 +6877,22 @@
     </row>
     <row r="126" ht="12.75" customHeight="1">
       <c r="A126" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B126" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="D126" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="C126" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="D126" s="5" t="s">
+      <c r="E126" s="17" t="s">
         <v>411</v>
       </c>
-      <c r="E126" s="17" t="s">
-        <v>412</v>
-      </c>
       <c r="F126" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G126" s="19"/>
       <c r="H126" s="7" t="s">
@@ -6901,7 +6905,7 @@
       <c r="K126" s="14"/>
       <c r="L126" s="18"/>
       <c r="M126" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N126" s="7" t="b">
         <v>1</v>
@@ -6911,25 +6915,25 @@
       </c>
     </row>
     <row r="127" ht="12.75" customHeight="1">
-      <c r="A127" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="B127" s="23" t="s">
+      <c r="A127" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B127" s="26" t="s">
+        <v>412</v>
+      </c>
+      <c r="C127" s="26" t="s">
+        <v>412</v>
+      </c>
+      <c r="D127" s="26" t="s">
         <v>413</v>
       </c>
-      <c r="C127" s="23" t="s">
-        <v>413</v>
-      </c>
-      <c r="D127" s="23" t="s">
+      <c r="E127" s="27" t="s">
         <v>414</v>
       </c>
-      <c r="E127" s="24" t="s">
-        <v>415</v>
-      </c>
-      <c r="F127" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="G127" s="25"/>
+      <c r="F127" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="G127" s="28"/>
       <c r="H127" s="7" t="s">
         <v>21</v>
       </c>
@@ -6938,9 +6942,9 @@
       </c>
       <c r="J127" s="14"/>
       <c r="K127" s="14"/>
-      <c r="L127" s="26"/>
+      <c r="L127" s="29"/>
       <c r="M127" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N127" s="7" t="b">
         <v>1</v>
